--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,6 +1603,721 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128846922</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92252</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tallåsen Ö Vattmossen, Möklinta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>585340</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6666597</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128846853</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79735</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tallåsen Ö Vattmossen, Möklinta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>585356</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6666605</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128846914</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tallåsen Ö Vattmossen, Möklinta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>585374</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6666695</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128846831</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79735</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tallåsen Ö Vattmossen, Möklinta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>585349</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6666537</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128846887</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tallåsen Ö Vattmossen, Möklinta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>585370</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6666672</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128846879</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tallåsen Ö Vattmossen, Möklinta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>585358</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6666581</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128846896</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tallåsen Ö Vattmossen, Möklinta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>585369</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6666729</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92252</v>
+        <v>92257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>128846853</v>
       </c>
       <c r="B12" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128846831</v>
       </c>
       <c r="B14" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92257</v>
+        <v>92262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92262</v>
+        <v>92266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>128846853</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128846831</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92266</v>
+        <v>92271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>128846853</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128846831</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92279</v>
+        <v>92284</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92284</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>128846853</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128846831</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>128846853</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128846831</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92842</v>
+        <v>92849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92842</v>
+        <v>92849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28069-2022 artfynd.xlsx
+++ b/artfynd/A 28069-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757421</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128758505</v>
       </c>
       <c r="B3" t="n">
-        <v>92849</v>
+        <v>92851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757546</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128757435</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128757027</v>
       </c>
       <c r="B6" t="n">
-        <v>92849</v>
+        <v>92851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128757558</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128757492</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128757650</v>
       </c>
       <c r="B9" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128757519</v>
       </c>
       <c r="B10" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128846922</v>
       </c>
       <c r="B11" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>128846853</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>128846914</v>
       </c>
       <c r="B13" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128846831</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>128846887</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128846879</v>
       </c>
       <c r="B16" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>128846896</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
